--- a/ValueSet-ACCESSUnalignmentResultVS.xlsx
+++ b/ValueSet-ACCESSUnalignmentResultVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T23:16:42-05:00</t>
+    <t>2026-03-06T16:03:26-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSUnalignmentResultVS.xlsx
+++ b/ValueSet-ACCESSUnalignmentResultVS.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSUnalignmentResultVS</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentResultVS</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T16:03:26-05:00</t>
+    <t>2026-03-12T23:55:37-07:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/CodeSystem/ACCESSUnalignmentResultCS</t>
+    <t>https://dsacms.github.io/cmmi-access-model/CodeSystem/ACCESSUnalignmentResultCS</t>
   </si>
 </sst>
 </file>

--- a/ValueSet-ACCESSUnalignmentResultVS.xlsx
+++ b/ValueSet-ACCESSUnalignmentResultVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T23:55:37-07:00</t>
+    <t>2026-04-24T13:45:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSUnalignmentResultVS.xlsx
+++ b/ValueSet-ACCESSUnalignmentResultVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSUnalignmentResultVS.xlsx
+++ b/ValueSet-ACCESSUnalignmentResultVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSUnalignmentResultVS.xlsx
+++ b/ValueSet-ACCESSUnalignmentResultVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSUnalignmentResultVS.xlsx
+++ b/ValueSet-ACCESSUnalignmentResultVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSUnalignmentResultVS.xlsx
+++ b/ValueSet-ACCESSUnalignmentResultVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
